--- a/public/demos/logistics/budget-vs-actual.xlsx
+++ b/public/demos/logistics/budget-vs-actual.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="GrossProfit_YTD">'Monthly Detail'!$F$38</definedName>
-    <definedName name="OperatingIncome_YTD">'Monthly Detail'!$F$40</definedName>
-    <definedName name="NetIncome_YTD">'Monthly Detail'!$F$42</definedName>
+    <definedName name="GrossProfit_YTD">'Monthly Detail'!$F$41</definedName>
+    <definedName name="OperatingIncome_YTD">'Monthly Detail'!$F$43</definedName>
+    <definedName name="NetIncome_YTD">'Monthly Detail'!$F$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Monthly Detail'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -810,7 +810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Acme Construction LLC</t>
+          <t>OSM Worldwide</t>
         </is>
       </c>
     </row>
@@ -893,14 +893,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Construction Revenue</t>
+          <t>Revenue - Chicago HQ</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1510000</v>
+        <v>3500000</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1500000</v>
+        <v>3400000</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
@@ -911,10 +911,10 @@
         <v/>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4315000</v>
+        <v>10350000</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>4200000</v>
+        <v>10125000</v>
       </c>
       <c r="H8" s="9">
         <f>F8-G8</f>
@@ -928,14 +928,14 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Service &amp; Maintenance Revenue</t>
+          <t>Revenue - Atlanta</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>78000</v>
+        <v>2333000</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>80000</v>
+        <v>2270000</v>
       </c>
       <c r="D9" s="13">
         <f>B9-C9</f>
@@ -946,10 +946,10 @@
         <v/>
       </c>
       <c r="F9" s="12" t="n">
-        <v>255000</v>
+        <v>6900000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>240000</v>
+        <v>6750000</v>
       </c>
       <c r="H9" s="13">
         <f>F9-G9</f>
@@ -961,248 +961,307 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Revenue - Dallas</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1940000</v>
+      </c>
+      <c r="D10" s="9">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(C10=0,0,D10/C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>5920000</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>5770000</v>
+      </c>
+      <c r="H10" s="9">
+        <f>F10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>IF(G10=0,0,H10/G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Revenue - Las Vegas</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="D11" s="13">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>IF(C11=0,0,D11/C11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>4430000</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>4330000</v>
+      </c>
+      <c r="H11" s="13">
+        <f>F11-G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>IF(G11=0,0,H11/G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Revenue - York PA</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1417000</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D12" s="9">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="10">
+        <f>IF(C12=0,0,D12/C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>4190000</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>4110000</v>
+      </c>
+      <c r="H12" s="9">
+        <f>F12-G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>IF(G12=0,0,H12/G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B10" s="16">
-        <f>SUM(B8:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="16">
-        <f>SUM(C8:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="17">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>IF(C10=0,0,D10/C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="16">
-        <f>SUM(F8:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="16">
-        <f>SUM(G8:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>F10-G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="18">
-        <f>IF(G10=0,0,H10/G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B13" s="16">
+        <f>SUM(B8:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>SUM(C8:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>IF(C13=0,0,D13/C13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>F13-G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="18">
+        <f>IF(G13=0,0,H13/G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Cost of Goods Sold</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Direct Labor</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>512000</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>510000</v>
-      </c>
-      <c r="D13" s="9">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(C13=0,0,D13/C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>1459000</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H13" s="9">
-        <f>F13-G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="10">
-        <f>IF(G13=0,0,H13/G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>442000</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>420000</v>
-      </c>
-      <c r="D14" s="13">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IF(C14=0,0,D14/C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>1255000</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>1176000</v>
-      </c>
-      <c r="H14" s="13">
-        <f>F14-G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>IF(G14=0,0,H14/G14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>248000</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>225000</v>
-      </c>
-      <c r="D15" s="9">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>IF(C15=0,0,D15/C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>663000</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>630000</v>
-      </c>
-      <c r="H15" s="9">
-        <f>F15-G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="10">
-        <f>IF(G15=0,0,H15/G15)</f>
-        <v/>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Equipment Costs</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Carrier &amp; Freight Costs</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>5913000</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>5748000</v>
+      </c>
+      <c r="D16" s="9">
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="10">
         <f>IF(C16=0,0,D16/C16)</f>
         <v/>
       </c>
-      <c r="F16" s="12" t="n">
-        <v>125500</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>126000</v>
-      </c>
-      <c r="H16" s="13">
+      <c r="F16" s="8" t="n">
+        <v>17484000</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>17097000</v>
+      </c>
+      <c r="H16" s="9">
         <f>F16-G16</f>
         <v/>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="10">
         <f>IF(G16=0,0,H16/G16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Total Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>SUM(B13:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="16">
-        <f>SUM(C13:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Sort &amp; Distribution Labor</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>1935000</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="D17" s="13">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="14">
         <f>IF(C17=0,0,D17/C17)</f>
         <v/>
       </c>
-      <c r="F17" s="16">
-        <f>SUM(F13:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>SUM(G13:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
+      <c r="F17" s="12" t="n">
+        <v>5722000</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>5595000</v>
+      </c>
+      <c r="H17" s="13">
         <f>F17-G17</f>
         <v/>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="14">
         <f>IF(G17=0,0,H17/G17)</f>
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Facility &amp; Warehouse Costs</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>538000</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>524000</v>
+      </c>
+      <c r="D18" s="9">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>IF(C18=0,0,D18/C18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>1589000</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1558000</v>
+      </c>
+      <c r="H18" s="9">
+        <f>F18-G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>IF(G18=0,0,H18/G18)</f>
+        <v/>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>161000</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>157000</v>
+      </c>
+      <c r="D19" s="13">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="14">
+        <f>IF(C19=0,0,D19/C19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>477000</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>466000</v>
+      </c>
+      <c r="H19" s="13">
+        <f>F19-G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>IF(G19=0,0,H19/G19)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Office Rent</t>
+          <t>Technology &amp; Tracking Systems</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>12000</v>
+        <v>108000</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>12000</v>
+        <v>105000</v>
       </c>
       <c r="D20" s="9">
         <f>B20-C20</f>
@@ -1213,10 +1272,10 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>36000</v>
+        <v>319000</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>36000</v>
+        <v>312000</v>
       </c>
       <c r="H20" s="9">
         <f>F20-G20</f>
@@ -1228,121 +1287,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Administrative Salaries</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>65000</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>62000</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Total Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>SUM(B16:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>SUM(C16:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="18">
         <f>IF(C21=0,0,D21/C21)</f>
         <v/>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>186000</v>
-      </c>
-      <c r="H21" s="13">
+      <c r="F21" s="16">
+        <f>SUM(F16:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>SUM(G16:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
         <f>F21-G21</f>
         <v/>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="18">
         <f>IF(G21=0,0,H21/G21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>27000</v>
-      </c>
-      <c r="D22" s="9">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(C22=0,0,D22/C22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>85500</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>81000</v>
-      </c>
-      <c r="H22" s="9">
-        <f>F22-G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="10">
-        <f>IF(G22=0,0,H22/G22)</f>
-        <v/>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Vehicle Expenses</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>19500</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D23" s="13">
-        <f>B23-C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="14">
-        <f>IF(C23=0,0,D23/C23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>54500</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H23" s="13">
-        <f>F23-G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="14">
-        <f>IF(G23=0,0,H23/G23)</f>
-        <v/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Office Supplies &amp; Software</t>
+          <t>Sales &amp; Account Management</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>5100</v>
+        <v>322000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>3500</v>
+        <v>314000</v>
       </c>
       <c r="D24" s="9">
         <f>B24-C24</f>
@@ -1353,10 +1353,10 @@
         <v/>
       </c>
       <c r="F24" s="8" t="n">
-        <v>13100</v>
+        <v>953000</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>10500</v>
+        <v>933000</v>
       </c>
       <c r="H24" s="9">
         <f>F24-G24</f>
@@ -1370,14 +1370,14 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>General &amp; Administrative</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>12000</v>
+        <v>269000</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5000</v>
+        <v>262000</v>
       </c>
       <c r="D25" s="13">
         <f>B25-C25</f>
@@ -1388,10 +1388,10 @@
         <v/>
       </c>
       <c r="F25" s="12" t="n">
-        <v>24700</v>
+        <v>795000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>15000</v>
+        <v>778000</v>
       </c>
       <c r="H25" s="13">
         <f>F25-G25</f>
@@ -1405,14 +1405,14 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t>IT &amp; Software</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>2800</v>
+        <v>161000</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3000</v>
+        <v>157000</v>
       </c>
       <c r="D26" s="9">
         <f>B26-C26</f>
@@ -1423,10 +1423,10 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>8500</v>
+        <v>477000</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>9000</v>
+        <v>466000</v>
       </c>
       <c r="H26" s="9">
         <f>F26-G26</f>
@@ -1440,14 +1440,14 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telephone</t>
+          <t>Insurance (Cargo &amp; General)</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>3400</v>
+        <v>108000</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>3500</v>
+        <v>99000</v>
       </c>
       <c r="D27" s="13">
         <f>B27-C27</f>
@@ -1458,10 +1458,10 @@
         <v/>
       </c>
       <c r="F27" s="12" t="n">
-        <v>10800</v>
+        <v>318000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>10500</v>
+        <v>294000</v>
       </c>
       <c r="H27" s="13">
         <f>F27-G27</f>
@@ -1473,320 +1473,425 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D28" s="9">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="10">
+        <f>IF(C28=0,0,D28/C28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>154000</v>
+      </c>
+      <c r="H28" s="9">
+        <f>F28-G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="10">
+        <f>IF(G28=0,0,H28/G28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>107000</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D29" s="13">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>IF(C29=0,0,D29/C29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>315000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>312000</v>
+      </c>
+      <c r="H29" s="13">
+        <f>F29-G29</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>IF(G29=0,0,H29/G29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D30" s="9">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(C30=0,0,D30/C30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>127000</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>124000</v>
+      </c>
+      <c r="H30" s="9">
+        <f>F30-G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="10">
+        <f>IF(G30=0,0,H30/G30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B28" s="16">
-        <f>SUM(B20:B27)</f>
-        <v/>
-      </c>
-      <c r="C28" s="16">
-        <f>SUM(C20:C27)</f>
-        <v/>
-      </c>
-      <c r="D28" s="17">
-        <f>B28-C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>IF(C28=0,0,D28/C28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="16">
-        <f>SUM(F20:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>SUM(G20:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="17">
-        <f>F28-G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IF(G28=0,0,H28/G28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B31" s="16">
+        <f>SUM(B24:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>SUM(C24:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
+        <f>IF(C31=0,0,D31/C31)</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>SUM(F24:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>SUM(G24:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>F31-G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="18">
+        <f>IF(G31=0,0,H31/G31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D31" s="9">
-        <f>B31-C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(C31=0,0,D31/C31)</f>
-        <v/>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>3650</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H31" s="9">
-        <f>F31-G31</f>
-        <v/>
-      </c>
-      <c r="I31" s="10">
-        <f>IF(G31=0,0,H31/G31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B34" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D34" s="9">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>IF(C34=0,0,D34/C34)</f>
+        <v/>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H34" s="9">
+        <f>F34-G34</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>IF(G34=0,0,H34/G34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Total Other Income</t>
         </is>
       </c>
-      <c r="B32" s="16">
-        <f>SUM(B31:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
-        <f>B32-C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="18">
-        <f>IF(C32=0,0,D32/C32)</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>SUM(G31:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="17">
-        <f>F32-G32</f>
-        <v/>
-      </c>
-      <c r="I32" s="18">
-        <f>IF(G32=0,0,H32/G32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="B35" s="16">
+        <f>SUM(B34:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>SUM(C34:C34)</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="18">
+        <f>IF(C35=0,0,D35/C35)</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>SUM(F34:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>SUM(G34:G34)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>F35-G35</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IF(G35=0,0,H35/G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D35" s="9">
-        <f>B35-C35</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>IF(C35=0,0,D35/C35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>14400</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H35" s="9">
-        <f>F35-G35</f>
-        <v/>
-      </c>
-      <c r="I35" s="10">
-        <f>IF(G35=0,0,H35/G35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="B38" s="8" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D38" s="9">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
+        <f>IF(C38=0,0,D38/C38)</f>
+        <v/>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>129000</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="H38" s="9">
+        <f>F38-G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="10">
+        <f>IF(G38=0,0,H38/G38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Total Other Expenses</t>
         </is>
       </c>
-      <c r="B36" s="16">
-        <f>SUM(B35:B35)</f>
-        <v/>
-      </c>
-      <c r="C36" s="16">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>B36-C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="18">
-        <f>IF(C36=0,0,D36/C36)</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>SUM(G35:G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="17">
-        <f>F36-G36</f>
-        <v/>
-      </c>
-      <c r="I36" s="18">
-        <f>IF(G36=0,0,H36/G36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="B39" s="16">
+        <f>SUM(B38:B38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>SUM(C38:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>B39-C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>IF(C39=0,0,D39/C39)</f>
+        <v/>
+      </c>
+      <c r="F39" s="16">
+        <f>SUM(F38:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="16">
+        <f>SUM(G38:G38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>F39-G39</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IF(G39=0,0,H39/G39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B38" s="20">
-        <f>B10-B17</f>
-        <v/>
-      </c>
-      <c r="C38" s="20">
-        <f>C10-C17</f>
-        <v/>
-      </c>
-      <c r="D38" s="21">
-        <f>B38-C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="22">
-        <f>IF(C38=0,0,D38/C38)</f>
-        <v/>
-      </c>
-      <c r="F38" s="20">
-        <f>F10-F17</f>
-        <v/>
-      </c>
-      <c r="G38" s="20">
-        <f>G10-G17</f>
-        <v/>
-      </c>
-      <c r="H38" s="21">
-        <f>F38-G38</f>
-        <v/>
-      </c>
-      <c r="I38" s="22">
-        <f>IF(G38=0,0,H38/G38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="B41" s="20">
+        <f>B13-B21</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f>C13-C21</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>B41-C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="22">
+        <f>IF(C41=0,0,D41/C41)</f>
+        <v/>
+      </c>
+      <c r="F41" s="20">
+        <f>F13-F21</f>
+        <v/>
+      </c>
+      <c r="G41" s="20">
+        <f>G13-G21</f>
+        <v/>
+      </c>
+      <c r="H41" s="21">
+        <f>F41-G41</f>
+        <v/>
+      </c>
+      <c r="I41" s="22">
+        <f>IF(G41=0,0,H41/G41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B40" s="20">
-        <f>B38-B28</f>
-        <v/>
-      </c>
-      <c r="C40" s="20">
-        <f>C38-C28</f>
-        <v/>
-      </c>
-      <c r="D40" s="21">
-        <f>B40-C40</f>
-        <v/>
-      </c>
-      <c r="E40" s="22">
-        <f>IF(C40=0,0,D40/C40)</f>
-        <v/>
-      </c>
-      <c r="F40" s="20">
-        <f>F38-F28</f>
-        <v/>
-      </c>
-      <c r="G40" s="20">
-        <f>G38-G28</f>
-        <v/>
-      </c>
-      <c r="H40" s="21">
-        <f>F40-G40</f>
-        <v/>
-      </c>
-      <c r="I40" s="22">
-        <f>IF(G40=0,0,H40/G40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="B43" s="20">
+        <f>B41-B31</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>C41-C31</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="22">
+        <f>IF(C43=0,0,D43/C43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>F41-F31</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f>G41-G31</f>
+        <v/>
+      </c>
+      <c r="H43" s="21">
+        <f>F43-G43</f>
+        <v/>
+      </c>
+      <c r="I43" s="22">
+        <f>IF(G43=0,0,H43/G43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B42" s="20">
-        <f>B40+B32-B36</f>
-        <v/>
-      </c>
-      <c r="C42" s="20">
-        <f>C40+C32-C36</f>
-        <v/>
-      </c>
-      <c r="D42" s="21">
-        <f>B42-C42</f>
-        <v/>
-      </c>
-      <c r="E42" s="22">
-        <f>IF(C42=0,0,D42/C42)</f>
-        <v/>
-      </c>
-      <c r="F42" s="20">
-        <f>F40+F32-F36</f>
-        <v/>
-      </c>
-      <c r="G42" s="20">
-        <f>G40+G32-G36</f>
-        <v/>
-      </c>
-      <c r="H42" s="21">
-        <f>F42-G42</f>
-        <v/>
-      </c>
-      <c r="I42" s="22">
-        <f>IF(G42=0,0,H42/G42)</f>
+      <c r="B45" s="20">
+        <f>B43+B35-B39</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f>C43+C35-C39</f>
+        <v/>
+      </c>
+      <c r="D45" s="21">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="22">
+        <f>IF(C45=0,0,D45/C45)</f>
+        <v/>
+      </c>
+      <c r="F45" s="20">
+        <f>F43+F35-F39</f>
+        <v/>
+      </c>
+      <c r="G45" s="20">
+        <f>G43+G35-G39</f>
+        <v/>
+      </c>
+      <c r="H45" s="21">
+        <f>F45-G45</f>
+        <v/>
+      </c>
+      <c r="I45" s="22">
+        <f>IF(G45=0,0,H45/G45)</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1902,7 @@
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7:E42">
+  <conditionalFormatting sqref="E7:E45">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.10</formula>
     </cfRule>
@@ -1813,7 +1918,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I42">
+  <conditionalFormatting sqref="I7:I45">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0.10</formula>
     </cfRule>
@@ -1866,7 +1971,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Acme Construction LLC</t>
+          <t>OSM Worldwide</t>
         </is>
       </c>
     </row>
@@ -1939,10 +2044,10 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>1588000</v>
+        <v>10750000</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1580000</v>
+        <v>10450000</v>
       </c>
       <c r="D6" s="25">
         <f>B6-C6</f>
@@ -1953,10 +2058,10 @@
         <v/>
       </c>
       <c r="F6" s="24" t="n">
-        <v>4570000</v>
+        <v>31790000</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>4440000</v>
+        <v>31085000</v>
       </c>
       <c r="H6" s="25">
         <f>F6-G6</f>
@@ -1974,10 +2079,10 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>1247000</v>
+        <v>8655000</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1200000</v>
+        <v>8414000</v>
       </c>
       <c r="D7" s="25">
         <f>B7-C7</f>
@@ -1988,10 +2093,10 @@
         <v/>
       </c>
       <c r="F7" s="24" t="n">
-        <v>3502500</v>
+        <v>25591000</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>3362000</v>
+        <v>25028000</v>
       </c>
       <c r="H7" s="25">
         <f>F7-G7</f>
@@ -2009,10 +2114,10 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>341000</v>
+        <v>2095000</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>380000</v>
+        <v>2036000</v>
       </c>
       <c r="D8" s="21">
         <f>B8-C8</f>
@@ -2023,10 +2128,10 @@
         <v/>
       </c>
       <c r="F8" s="20" t="n">
-        <v>1067500</v>
+        <v>6199000</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>1078000</v>
+        <v>6057000</v>
       </c>
       <c r="H8" s="21">
         <f>F8-G8</f>
@@ -2044,10 +2149,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>148300</v>
+        <v>1064000</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>131000</v>
+        <v>1031000</v>
       </c>
       <c r="D9" s="25">
         <f>B9-C9</f>
@@ -2058,10 +2163,10 @@
         <v/>
       </c>
       <c r="F9" s="24" t="n">
-        <v>428100</v>
+        <v>3144000</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>393000</v>
+        <v>3061000</v>
       </c>
       <c r="H9" s="25">
         <f>F9-G9</f>
@@ -2079,10 +2184,10 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>192700</v>
+        <v>1031000</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>249000</v>
+        <v>1005000</v>
       </c>
       <c r="D10" s="21">
         <f>B10-C10</f>
@@ -2093,10 +2198,10 @@
         <v/>
       </c>
       <c r="F10" s="20" t="n">
-        <v>639400</v>
+        <v>3055000</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>685000</v>
+        <v>2996000</v>
       </c>
       <c r="H10" s="21">
         <f>F10-G10</f>
@@ -2114,10 +2219,10 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>189000</v>
+        <v>1001000</v>
       </c>
       <c r="C11" s="20" t="n">
-        <v>245000</v>
+        <v>970000</v>
       </c>
       <c r="D11" s="21">
         <f>B11-C11</f>
@@ -2128,10 +2233,10 @@
         <v/>
       </c>
       <c r="F11" s="20" t="n">
-        <v>628650</v>
+        <v>2961000</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>673000</v>
+        <v>2891000</v>
       </c>
       <c r="H11" s="21">
         <f>F11-G11</f>
@@ -2184,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2205,7 +2310,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Acme Construction LLC</t>
+          <t>OSM Worldwide</t>
         </is>
       </c>
     </row>
@@ -2301,14 +2406,14 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>Construction Revenue</t>
+          <t>Revenue - Chicago HQ</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4315000</v>
+        <v>10350000</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>4200000</v>
+        <v>10125000</v>
       </c>
       <c r="D7" s="10">
         <f>IF(C7=0,0,(B7-C7)/C7)</f>
@@ -2318,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4800000</v>
+        <v>10600000</v>
       </c>
       <c r="G7" s="10">
         <f>IF(F7=0,0,(E7-F7)/F7)</f>
@@ -2328,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>5250000</v>
+        <v>10950000</v>
       </c>
       <c r="J7" s="10">
         <f>IF(I7=0,0,(H7-I7)/I7)</f>
@@ -2338,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4050000</v>
+        <v>11300000</v>
       </c>
       <c r="M7" s="10">
         <f>IF(L7=0,0,(K7-L7)/L7)</f>
@@ -2348,14 +2453,14 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Service &amp; Maintenance Revenue</t>
+          <t>Revenue - Atlanta</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>255000</v>
+        <v>6900000</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>240000</v>
+        <v>6750000</v>
       </c>
       <c r="D8" s="14">
         <f>IF(C8=0,0,(B8-C8)/C8)</f>
@@ -2365,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>260000</v>
+        <v>7070000</v>
       </c>
       <c r="G8" s="14">
         <f>IF(F8=0,0,(E8-F8)/F8)</f>
@@ -2375,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>265000</v>
+        <v>7300000</v>
       </c>
       <c r="J8" s="14">
         <f>IF(I8=0,0,(H8-I8)/I8)</f>
@@ -2385,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>230000</v>
+        <v>7520000</v>
       </c>
       <c r="M8" s="14">
         <f>IF(L8=0,0,(K8-L8)/L8)</f>
@@ -2393,328 +2498,407 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Revenue - Dallas</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>5920000</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>5770000</v>
+      </c>
+      <c r="D9" s="10">
+        <f>IF(C9=0,0,(B9-C9)/C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>6060000</v>
+      </c>
+      <c r="G9" s="10">
+        <f>IF(F9=0,0,(E9-F9)/F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>6260000</v>
+      </c>
+      <c r="J9" s="10">
+        <f>IF(I9=0,0,(H9-I9)/I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>6450000</v>
+      </c>
+      <c r="M9" s="10">
+        <f>IF(L9=0,0,(K9-L9)/L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Revenue - Las Vegas</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>4430000</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>4330000</v>
+      </c>
+      <c r="D10" s="14">
+        <f>IF(C10=0,0,(B10-C10)/C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="G10" s="14">
+        <f>IF(F10=0,0,(E10-F10)/F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>4690000</v>
+      </c>
+      <c r="J10" s="14">
+        <f>IF(I10=0,0,(H10-I10)/I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>4840000</v>
+      </c>
+      <c r="M10" s="14">
+        <f>IF(L10=0,0,(K10-L10)/L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Revenue - York PA</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>4190000</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>4110000</v>
+      </c>
+      <c r="D11" s="10">
+        <f>IF(C11=0,0,(B11-C11)/C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="G11" s="10">
+        <f>IF(F11=0,0,(E11-F11)/F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>4440000</v>
+      </c>
+      <c r="J11" s="10">
+        <f>IF(I11=0,0,(H11-I11)/I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="M11" s="10">
+        <f>IF(L11=0,0,(K11-L11)/L11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B9" s="16">
-        <f>SUM(B7:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
-        <f>SUM(C7:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
-        <f>IF(C9=0,0,(B9-C9)/C9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="16">
-        <f>SUM(E7:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
-        <f>SUM(F7:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="18">
-        <f>IF(F9=0,0,(E9-F9)/F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
-        <f>SUM(H7:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="16">
-        <f>SUM(I7:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="18">
-        <f>IF(I9=0,0,(H9-I9)/I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
-        <f>SUM(K7:K8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="16">
-        <f>SUM(L7:L8)</f>
-        <v/>
-      </c>
-      <c r="M9" s="18">
-        <f>IF(L9=0,0,(K9-L9)/L9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B12" s="16">
+        <f>SUM(B7:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>SUM(C7:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>IF(C12=0,0,(B12-C12)/C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>SUM(E7:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>SUM(F7:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>IF(F12=0,0,(E12-F12)/F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>SUM(H7:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="16">
+        <f>SUM(I7:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <f>IF(I12=0,0,(H12-I12)/I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="16">
+        <f>SUM(K7:K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="16">
+        <f>SUM(L7:L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="18">
+        <f>IF(L12=0,0,(K12-L12)/L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Cost of Goods Sold</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Direct Labor</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1459000</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="D12" s="10">
-        <f>IF(C12=0,0,(B12-C12)/C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>1630000</v>
-      </c>
-      <c r="G12" s="10">
-        <f>IF(F12=0,0,(E12-F12)/F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>1784000</v>
-      </c>
-      <c r="J12" s="10">
-        <f>IF(I12=0,0,(H12-I12)/I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>1378000</v>
-      </c>
-      <c r="M12" s="10">
-        <f>IF(L12=0,0,(K12-L12)/L12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>1255000</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1176000</v>
-      </c>
-      <c r="D13" s="14">
-        <f>IF(C13=0,0,(B13-C13)/C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>1344000</v>
-      </c>
-      <c r="G13" s="14">
-        <f>IF(F13=0,0,(E13-F13)/F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>1470000</v>
-      </c>
-      <c r="J13" s="14">
-        <f>IF(I13=0,0,(H13-I13)/I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>1134000</v>
-      </c>
-      <c r="M13" s="14">
-        <f>IF(L13=0,0,(K13-L13)/L13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>663000</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>630000</v>
-      </c>
-      <c r="D14" s="10">
-        <f>IF(C14=0,0,(B14-C14)/C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>720000</v>
-      </c>
-      <c r="G14" s="10">
-        <f>IF(F14=0,0,(E14-F14)/F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>787500</v>
-      </c>
-      <c r="J14" s="10">
-        <f>IF(I14=0,0,(H14-I14)/I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>607500</v>
-      </c>
-      <c r="M14" s="10">
-        <f>IF(L14=0,0,(K14-L14)/L14)</f>
-        <v/>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Equipment Costs</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>125500</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>126000</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Carrier &amp; Freight Costs</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>17484000</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>17097000</v>
+      </c>
+      <c r="D15" s="10">
         <f>IF(C15=0,0,(B15-C15)/C15)</f>
         <v/>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>144000</v>
-      </c>
-      <c r="G15" s="14">
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>17911000</v>
+      </c>
+      <c r="G15" s="10">
         <f>IF(F15=0,0,(E15-F15)/F15)</f>
         <v/>
       </c>
-      <c r="H15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>157500</v>
-      </c>
-      <c r="J15" s="14">
+      <c r="H15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>18520000</v>
+      </c>
+      <c r="J15" s="10">
         <f>IF(I15=0,0,(H15-I15)/I15)</f>
         <v/>
       </c>
-      <c r="K15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>121500</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="K15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>19084000</v>
+      </c>
+      <c r="M15" s="10">
         <f>IF(L15=0,0,(K15-L15)/L15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Total Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B16" s="16">
-        <f>SUM(B12:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="16">
-        <f>SUM(C12:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Sort &amp; Distribution Labor</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>5722000</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>5595000</v>
+      </c>
+      <c r="D16" s="14">
         <f>IF(C16=0,0,(B16-C16)/C16)</f>
         <v/>
       </c>
-      <c r="E16" s="16">
-        <f>SUM(E12:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="16">
-        <f>SUM(F12:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="18">
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>5861000</v>
+      </c>
+      <c r="G16" s="14">
         <f>IF(F16=0,0,(E16-F16)/F16)</f>
         <v/>
       </c>
-      <c r="H16" s="16">
-        <f>SUM(H12:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="16">
-        <f>SUM(I12:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="18">
+      <c r="H16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>6061000</v>
+      </c>
+      <c r="J16" s="14">
         <f>IF(I16=0,0,(H16-I16)/I16)</f>
         <v/>
       </c>
-      <c r="K16" s="16">
-        <f>SUM(K12:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="16">
-        <f>SUM(L12:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="18">
+      <c r="K16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>6243000</v>
+      </c>
+      <c r="M16" s="14">
         <f>IF(L16=0,0,(K16-L16)/L16)</f>
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Facility &amp; Warehouse Costs</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1589000</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>1558000</v>
+      </c>
+      <c r="D17" s="10">
+        <f>IF(C17=0,0,(B17-C17)/C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1633000</v>
+      </c>
+      <c r="G17" s="10">
+        <f>IF(F17=0,0,(E17-F17)/F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1688000</v>
+      </c>
+      <c r="J17" s="10">
+        <f>IF(I17=0,0,(H17-I17)/I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>1739000</v>
+      </c>
+      <c r="M17" s="10">
+        <f>IF(L17=0,0,(K17-L17)/L17)</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>477000</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>466000</v>
+      </c>
+      <c r="D18" s="14">
+        <f>IF(C18=0,0,(B18-C18)/C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>489000</v>
+      </c>
+      <c r="G18" s="14">
+        <f>IF(F18=0,0,(E18-F18)/F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>505000</v>
+      </c>
+      <c r="J18" s="14">
+        <f>IF(I18=0,0,(H18-I18)/I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>520000</v>
+      </c>
+      <c r="M18" s="14">
+        <f>IF(L18=0,0,(K18-L18)/L18)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>Office Rent</t>
+          <t>Technology &amp; Tracking Systems</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>36000</v>
+        <v>319000</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>36000</v>
+        <v>312000</v>
       </c>
       <c r="D19" s="10">
         <f>IF(C19=0,0,(B19-C19)/C19)</f>
@@ -2724,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>36000</v>
+        <v>326000</v>
       </c>
       <c r="G19" s="10">
         <f>IF(F19=0,0,(E19-F19)/F19)</f>
@@ -2734,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>36000</v>
+        <v>337000</v>
       </c>
       <c r="J19" s="10">
         <f>IF(I19=0,0,(H19-I19)/I19)</f>
@@ -2744,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>36000</v>
+        <v>348000</v>
       </c>
       <c r="M19" s="10">
         <f>IF(L19=0,0,(K19-L19)/L19)</f>
@@ -2752,157 +2936,78 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Administrative Salaries</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>186000</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Total Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>SUM(B15:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>SUM(C15:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
         <f>IF(C20=0,0,(B20-C20)/C20)</f>
         <v/>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="G20" s="14">
+      <c r="E20" s="16">
+        <f>SUM(E15:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f>SUM(F15:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="18">
         <f>IF(F20=0,0,(E20-F20)/F20)</f>
         <v/>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="J20" s="14">
+      <c r="H20" s="16">
+        <f>SUM(H15:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="16">
+        <f>SUM(I15:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="18">
         <f>IF(I20=0,0,(H20-I20)/I20)</f>
         <v/>
       </c>
-      <c r="K20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>195000</v>
-      </c>
-      <c r="M20" s="14">
+      <c r="K20" s="16">
+        <f>SUM(K15:K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="16">
+        <f>SUM(L15:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="18">
         <f>IF(L20=0,0,(K20-L20)/L20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>85500</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>81000</v>
-      </c>
-      <c r="D21" s="10">
-        <f>IF(C21=0,0,(B21-C21)/C21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>81000</v>
-      </c>
-      <c r="G21" s="10">
-        <f>IF(F21=0,0,(E21-F21)/F21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>81000</v>
-      </c>
-      <c r="J21" s="10">
-        <f>IF(I21=0,0,(H21-I21)/I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>81000</v>
-      </c>
-      <c r="M21" s="10">
-        <f>IF(L21=0,0,(K21-L21)/L21)</f>
-        <v/>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>Vehicle Expenses</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>54500</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D22" s="14">
-        <f>IF(C22=0,0,(B22-C22)/C22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>51000</v>
-      </c>
-      <c r="G22" s="14">
-        <f>IF(F22=0,0,(E22-F22)/F22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>51000</v>
-      </c>
-      <c r="J22" s="14">
-        <f>IF(I22=0,0,(H22-I22)/I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="M22" s="14">
-        <f>IF(L22=0,0,(K22-L22)/L22)</f>
-        <v/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Office Supplies &amp; Software</t>
+          <t>Sales &amp; Account Management</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>13100</v>
+        <v>953000</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>10500</v>
+        <v>933000</v>
       </c>
       <c r="D23" s="10">
         <f>IF(C23=0,0,(B23-C23)/C23)</f>
@@ -2912,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>10500</v>
+        <v>977000</v>
       </c>
       <c r="G23" s="10">
         <f>IF(F23=0,0,(E23-F23)/F23)</f>
@@ -2922,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>10500</v>
+        <v>1011000</v>
       </c>
       <c r="J23" s="10">
         <f>IF(I23=0,0,(H23-I23)/I23)</f>
@@ -2932,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>10500</v>
+        <v>1040000</v>
       </c>
       <c r="M23" s="10">
         <f>IF(L23=0,0,(K23-L23)/L23)</f>
@@ -2942,14 +3047,14 @@
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>General &amp; Administrative</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>24700</v>
+        <v>795000</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>15000</v>
+        <v>778000</v>
       </c>
       <c r="D24" s="14">
         <f>IF(C24=0,0,(B24-C24)/C24)</f>
@@ -2959,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>15000</v>
+        <v>815000</v>
       </c>
       <c r="G24" s="14">
         <f>IF(F24=0,0,(E24-F24)/F24)</f>
@@ -2969,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>15000</v>
+        <v>843000</v>
       </c>
       <c r="J24" s="14">
         <f>IF(I24=0,0,(H24-I24)/I24)</f>
@@ -2979,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>15000</v>
+        <v>868000</v>
       </c>
       <c r="M24" s="14">
         <f>IF(L24=0,0,(K24-L24)/L24)</f>
@@ -2989,14 +3094,14 @@
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>Advertising &amp; Marketing</t>
+          <t>IT &amp; Software</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>8500</v>
+        <v>477000</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>9000</v>
+        <v>466000</v>
       </c>
       <c r="D25" s="10">
         <f>IF(C25=0,0,(B25-C25)/C25)</f>
@@ -3006,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>11000</v>
+        <v>489000</v>
       </c>
       <c r="G25" s="10">
         <f>IF(F25=0,0,(E25-F25)/F25)</f>
@@ -3016,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>11000</v>
+        <v>505000</v>
       </c>
       <c r="J25" s="10">
         <f>IF(I25=0,0,(H25-I25)/I25)</f>
@@ -3026,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>9000</v>
+        <v>520000</v>
       </c>
       <c r="M25" s="10">
         <f>IF(L25=0,0,(K25-L25)/L25)</f>
@@ -3036,14 +3141,14 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>Utilities &amp; Telephone</t>
+          <t>Insurance (Cargo &amp; General)</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>10800</v>
+        <v>318000</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>10500</v>
+        <v>294000</v>
       </c>
       <c r="D26" s="14">
         <f>IF(C26=0,0,(B26-C26)/C26)</f>
@@ -3053,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>10500</v>
+        <v>307000</v>
       </c>
       <c r="G26" s="14">
         <f>IF(F26=0,0,(E26-F26)/F26)</f>
@@ -3063,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>10500</v>
+        <v>318000</v>
       </c>
       <c r="J26" s="14">
         <f>IF(I26=0,0,(H26-I26)/I26)</f>
@@ -3073,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>10500</v>
+        <v>326000</v>
       </c>
       <c r="M26" s="14">
         <f>IF(L26=0,0,(K26-L26)/L26)</f>
@@ -3081,275 +3186,416 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>159000</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>154000</v>
+      </c>
+      <c r="D27" s="10">
+        <f>IF(C27=0,0,(B27-C27)/C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>162000</v>
+      </c>
+      <c r="G27" s="10">
+        <f>IF(F27=0,0,(E27-F27)/F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>168000</v>
+      </c>
+      <c r="J27" s="10">
+        <f>IF(I27=0,0,(H27-I27)/I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>172000</v>
+      </c>
+      <c r="M27" s="10">
+        <f>IF(L27=0,0,(K27-L27)/L27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>315000</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>312000</v>
+      </c>
+      <c r="D28" s="14">
+        <f>IF(C28=0,0,(B28-C28)/C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>326000</v>
+      </c>
+      <c r="G28" s="14">
+        <f>IF(F28=0,0,(E28-F28)/F28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>337000</v>
+      </c>
+      <c r="J28" s="14">
+        <f>IF(I28=0,0,(H28-I28)/I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>348000</v>
+      </c>
+      <c r="M28" s="14">
+        <f>IF(L28=0,0,(K28-L28)/L28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>127000</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>124000</v>
+      </c>
+      <c r="D29" s="10">
+        <f>IF(C29=0,0,(B29-C29)/C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="G29" s="10">
+        <f>IF(F29=0,0,(E29-F29)/F29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="J29" s="10">
+        <f>IF(I29=0,0,(H29-I29)/I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>138000</v>
+      </c>
+      <c r="M29" s="10">
+        <f>IF(L29=0,0,(K29-L29)/L29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B27" s="16">
-        <f>SUM(B19:B26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="16">
-        <f>SUM(C19:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IF(C27=0,0,(B27-C27)/C27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="16">
-        <f>SUM(E19:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="16">
-        <f>SUM(F19:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IF(F27=0,0,(E27-F27)/F27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="16">
-        <f>SUM(H19:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="16">
-        <f>SUM(I19:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="18">
-        <f>IF(I27=0,0,(H27-I27)/I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="16">
-        <f>SUM(K19:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="16">
-        <f>SUM(L19:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="18">
-        <f>IF(L27=0,0,(K27-L27)/L27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="B30" s="16">
+        <f>SUM(B23:B29)</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>SUM(C23:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>IF(C30=0,0,(B30-C30)/C30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>SUM(E23:E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>SUM(F23:F29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="18">
+        <f>IF(F30=0,0,(E30-F30)/F30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>SUM(H23:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>SUM(I23:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="18">
+        <f>IF(I30=0,0,(H30-I30)/I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
+        <f>SUM(K23:K29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="16">
+        <f>SUM(L23:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="18">
+        <f>IF(L30=0,0,(K30-L30)/L30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D30" s="10">
-        <f>IF(C30=0,0,(B30-C30)/C30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G30" s="10">
-        <f>IF(F30=0,0,(E30-F30)/F30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J30" s="10">
-        <f>IF(I30=0,0,(H30-I30)/I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M30" s="10">
-        <f>IF(L30=0,0,(K30-L30)/L30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B33" s="8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D33" s="10">
+        <f>IF(C33=0,0,(B33-C33)/C33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G33" s="10">
+        <f>IF(F33=0,0,(E33-F33)/F33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J33" s="10">
+        <f>IF(I33=0,0,(H33-I33)/I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M33" s="10">
+        <f>IF(L33=0,0,(K33-L33)/L33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Total Other Income</t>
         </is>
       </c>
-      <c r="B31" s="16">
-        <f>SUM(B30:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="16">
-        <f>SUM(C30:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f>IF(C31=0,0,(B31-C31)/C31)</f>
-        <v/>
-      </c>
-      <c r="E31" s="16">
-        <f>SUM(E30:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="16">
-        <f>SUM(F30:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="18">
-        <f>IF(F31=0,0,(E31-F31)/F31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="16">
-        <f>SUM(H30:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="16">
-        <f>SUM(I30:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="18">
-        <f>IF(I31=0,0,(H31-I31)/I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="16">
-        <f>SUM(K30:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="16">
-        <f>SUM(L30:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="18">
-        <f>IF(L31=0,0,(K31-L31)/L31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B34" s="16">
+        <f>SUM(B33:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>SUM(C33:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>IF(C34=0,0,(B34-C34)/C34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>SUM(E33:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="16">
+        <f>SUM(F33:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>IF(F34=0,0,(E34-F34)/F34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="16">
+        <f>SUM(H33:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="16">
+        <f>SUM(I33:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>IF(I34=0,0,(H34-I34)/I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
+        <f>SUM(K33:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="16">
+        <f>SUM(L33:L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="18">
+        <f>IF(L34=0,0,(K34-L34)/L34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>14400</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D34" s="10">
-        <f>IF(C34=0,0,(B34-C34)/C34)</f>
-        <v/>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G34" s="10">
-        <f>IF(F34=0,0,(E34-F34)/F34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J34" s="10">
-        <f>IF(I34=0,0,(H34-I34)/I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M34" s="10">
-        <f>IF(L34=0,0,(K34-L34)/L34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B37" s="8" t="n">
+        <v>129000</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="D37" s="10">
+        <f>IF(C37=0,0,(B37-C37)/C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="G37" s="10">
+        <f>IF(F37=0,0,(E37-F37)/F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="J37" s="10">
+        <f>IF(I37=0,0,(H37-I37)/I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>135000</v>
+      </c>
+      <c r="M37" s="10">
+        <f>IF(L37=0,0,(K37-L37)/L37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Total Other Expenses</t>
         </is>
       </c>
-      <c r="B35" s="16">
-        <f>SUM(B34:B34)</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="18">
-        <f>IF(C35=0,0,(B35-C35)/C35)</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>SUM(E34:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="18">
-        <f>IF(F35=0,0,(E35-F35)/F35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>SUM(H34:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="16">
-        <f>SUM(I34:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="18">
-        <f>IF(I35=0,0,(H35-I35)/I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="16">
-        <f>SUM(K34:K34)</f>
-        <v/>
-      </c>
-      <c r="L35" s="16">
-        <f>SUM(L34:L34)</f>
-        <v/>
-      </c>
-      <c r="M35" s="18">
-        <f>IF(L35=0,0,(K35-L35)/L35)</f>
+      <c r="B38" s="16">
+        <f>SUM(B37:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="16">
+        <f>SUM(C37:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>IF(C38=0,0,(B38-C38)/C38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="16">
+        <f>SUM(E37:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="16">
+        <f>SUM(F37:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="18">
+        <f>IF(F38=0,0,(E38-F38)/F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="16">
+        <f>SUM(H37:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="16">
+        <f>SUM(I37:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="18">
+        <f>IF(I38=0,0,(H38-I38)/I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="16">
+        <f>SUM(K37:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="16">
+        <f>SUM(L37:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="18">
+        <f>IF(L38=0,0,(K38-L38)/L38)</f>
         <v/>
       </c>
     </row>
@@ -3359,7 +3605,7 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D37">
+  <conditionalFormatting sqref="D6:D40">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3367,7 +3613,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G37">
+  <conditionalFormatting sqref="G6:G40">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3375,7 +3621,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J37">
+  <conditionalFormatting sqref="J6:J40">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3383,7 +3629,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M37">
+  <conditionalFormatting sqref="M6:M40">
     <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3424,7 +3670,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Acme Construction LLC</t>
+          <t>OSM Worldwide</t>
         </is>
       </c>
     </row>
@@ -3517,13 +3763,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1505000</v>
+        <v>10290000</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1477000</v>
+        <v>10750000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1588000</v>
+        <v>10750000</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0</v>
@@ -3560,40 +3806,40 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1430000</v>
+        <v>10280000</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1430000</v>
+        <v>10355000</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1580000</v>
+        <v>10450000</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1585000</v>
+        <v>10600000</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1735000</v>
+        <v>10910000</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>1740000</v>
+        <v>11060000</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1890000</v>
+        <v>11200000</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>1890000</v>
+        <v>11380000</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>1735000</v>
+        <v>11060000</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>1580000</v>
+        <v>10750000</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1425000</v>
+        <v>11670000</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>1275000</v>
+        <v>12270000</v>
       </c>
     </row>
     <row r="8">
@@ -3658,13 +3904,13 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>360000</v>
+        <v>1978000</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>366500</v>
+        <v>2126000</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>341000</v>
+        <v>2095000</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>0</v>
@@ -3701,40 +3947,40 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>349000</v>
+        <v>2003000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>349000</v>
+        <v>2018000</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>380000</v>
+        <v>2036000</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>385000</v>
+        <v>2066000</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>416000</v>
+        <v>2129000</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>421000</v>
+        <v>2155000</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>450000</v>
+        <v>2171000</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>450000</v>
+        <v>2203000</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>416000</v>
+        <v>2155000</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>380000</v>
+        <v>2094000</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>344000</v>
+        <v>2271000</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>315000</v>
+        <v>2391000</v>
       </c>
     </row>
     <row r="11">
@@ -3799,13 +4045,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>217300</v>
+        <v>937000</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>229400</v>
+        <v>1087000</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>192700</v>
+        <v>1031000</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>0</v>
@@ -3842,40 +4088,40 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>218000</v>
+        <v>992000</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>218000</v>
+        <v>999000</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>249000</v>
+        <v>1005000</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>251000</v>
+        <v>1023000</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>278000</v>
+        <v>1055000</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>283000</v>
+        <v>1066000</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>312000</v>
+        <v>1066000</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>312000</v>
+        <v>1080000</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>282000</v>
+        <v>1066000</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>246000</v>
+        <v>1037000</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>210000</v>
+        <v>1123000</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>181000</v>
+        <v>1184000</v>
       </c>
     </row>
     <row r="14">
@@ -3940,13 +4186,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>213700</v>
+        <v>904000</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>225950</v>
+        <v>1056000</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>189000</v>
+        <v>1001000</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
@@ -3983,40 +4229,40 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>214000</v>
+        <v>957000</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>214000</v>
+        <v>964000</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>245000</v>
+        <v>970000</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>247000</v>
+        <v>988000</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>274000</v>
+        <v>1020000</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>279000</v>
+        <v>1031000</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>308000</v>
+        <v>1031000</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>308000</v>
+        <v>1045000</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>278000</v>
+        <v>1031000</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>242000</v>
+        <v>1002000</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>206000</v>
+        <v>1088000</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>177000</v>
+        <v>1149000</v>
       </c>
     </row>
     <row r="17">

--- a/public/demos/logistics/budget-vs-actual.xlsx
+++ b/public/demos/logistics/budget-vs-actual.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="GrossProfit_YTD">'Monthly Detail'!$F$41</definedName>
-    <definedName name="OperatingIncome_YTD">'Monthly Detail'!$F$43</definedName>
-    <definedName name="NetIncome_YTD">'Monthly Detail'!$F$45</definedName>
+    <definedName name="GrossProfit_YTD">'Monthly Detail'!$F$38</definedName>
+    <definedName name="OperatingIncome_YTD">'Monthly Detail'!$F$40</definedName>
+    <definedName name="NetIncome_YTD">'Monthly Detail'!$F$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Monthly Detail'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -810,7 +810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSM Worldwide</t>
+          <t>Acme Construction LLC</t>
         </is>
       </c>
     </row>
@@ -893,14 +893,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Revenue - Chicago HQ</t>
+          <t>Construction Revenue</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3500000</v>
+        <v>1510000</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3400000</v>
+        <v>1500000</v>
       </c>
       <c r="D8" s="9">
         <f>B8-C8</f>
@@ -911,10 +911,10 @@
         <v/>
       </c>
       <c r="F8" s="8" t="n">
-        <v>10350000</v>
+        <v>4315000</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>10125000</v>
+        <v>4200000</v>
       </c>
       <c r="H8" s="9">
         <f>F8-G8</f>
@@ -928,14 +928,14 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Revenue - Atlanta</t>
+          <t>Service &amp; Maintenance Revenue</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2333000</v>
+        <v>78000</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>2270000</v>
+        <v>80000</v>
       </c>
       <c r="D9" s="13">
         <f>B9-C9</f>
@@ -946,10 +946,10 @@
         <v/>
       </c>
       <c r="F9" s="12" t="n">
-        <v>6900000</v>
+        <v>255000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>6750000</v>
+        <v>240000</v>
       </c>
       <c r="H9" s="13">
         <f>F9-G9</f>
@@ -961,307 +961,248 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Revenue - Dallas</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1940000</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>SUM(B8:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>SUM(C8:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="18">
         <f>IF(C10=0,0,D10/C10)</f>
         <v/>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>5920000</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>5770000</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="F10" s="16">
+        <f>SUM(F8:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>SUM(G8:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="18">
         <f>IF(G10=0,0,H10/G10)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Revenue - Las Vegas</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>1460000</v>
-      </c>
-      <c r="D11" s="13">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
-        <f>IF(C11=0,0,D11/C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>4430000</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>4330000</v>
-      </c>
-      <c r="H11" s="13">
-        <f>F11-G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="14">
-        <f>IF(G11=0,0,H11/G11)</f>
-        <v/>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Revenue - York PA</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1417000</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>1380000</v>
-      </c>
-      <c r="D12" s="9">
-        <f>B12-C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>IF(C12=0,0,D12/C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>4190000</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>4110000</v>
-      </c>
-      <c r="H12" s="9">
-        <f>F12-G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="10">
-        <f>IF(G12=0,0,H12/G12)</f>
-        <v/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
-        <f>SUM(B8:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
-        <f>SUM(C8:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Direct Labor</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>512000</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>510000</v>
+      </c>
+      <c r="D13" s="9">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="10">
         <f>IF(C13=0,0,D13/C13)</f>
         <v/>
       </c>
-      <c r="F13" s="16">
-        <f>SUM(F8:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>SUM(G8:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
+      <c r="F13" s="8" t="n">
+        <v>1459000</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H13" s="9">
         <f>F13-G13</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="10">
         <f>IF(G13=0,0,H13/G13)</f>
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>442000</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>420000</v>
+      </c>
+      <c r="D14" s="13">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>IF(C14=0,0,D14/C14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>1255000</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>1176000</v>
+      </c>
+      <c r="H14" s="13">
+        <f>F14-G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>IF(G14=0,0,H14/G14)</f>
+        <v/>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>248000</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>225000</v>
+      </c>
+      <c r="D15" s="9">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(C15=0,0,D15/C15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>663000</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>630000</v>
+      </c>
+      <c r="H15" s="9">
+        <f>F15-G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="10">
+        <f>IF(G15=0,0,H15/G15)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Carrier &amp; Freight Costs</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>5913000</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>5748000</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Equipment Costs</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D16" s="13">
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="14">
         <f>IF(C16=0,0,D16/C16)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>17484000</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>17097000</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="F16" s="12" t="n">
+        <v>125500</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>126000</v>
+      </c>
+      <c r="H16" s="13">
         <f>F16-G16</f>
         <v/>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="14">
         <f>IF(G16=0,0,H16/G16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Sort &amp; Distribution Labor</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>1935000</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>1880000</v>
-      </c>
-      <c r="D17" s="13">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Total Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>SUM(B13:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="18">
         <f>IF(C17=0,0,D17/C17)</f>
         <v/>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>5722000</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>5595000</v>
-      </c>
-      <c r="H17" s="13">
+      <c r="F17" s="16">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>SUM(G13:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
         <f>F17-G17</f>
         <v/>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="18">
         <f>IF(G17=0,0,H17/G17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Facility &amp; Warehouse Costs</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>538000</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>524000</v>
-      </c>
-      <c r="D18" s="9">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>IF(C18=0,0,D18/C18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>1589000</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>1558000</v>
-      </c>
-      <c r="H18" s="9">
-        <f>F18-G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="10">
-        <f>IF(G18=0,0,H18/G18)</f>
-        <v/>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Packaging &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>161000</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>157000</v>
-      </c>
-      <c r="D19" s="13">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="14">
-        <f>IF(C19=0,0,D19/C19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>477000</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>466000</v>
-      </c>
-      <c r="H19" s="13">
-        <f>F19-G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="14">
-        <f>IF(G19=0,0,H19/G19)</f>
-        <v/>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Technology &amp; Tracking Systems</t>
+          <t>Office Rent</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>108000</v>
+        <v>12000</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>105000</v>
+        <v>12000</v>
       </c>
       <c r="D20" s="9">
         <f>B20-C20</f>
@@ -1272,10 +1213,10 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>319000</v>
+        <v>36000</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>312000</v>
+        <v>36000</v>
       </c>
       <c r="H20" s="9">
         <f>F20-G20</f>
@@ -1287,62 +1228,121 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Total Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>SUM(B16:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>SUM(C16:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="17">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Administrative Salaries</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>62000</v>
+      </c>
+      <c r="D21" s="13">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="14">
         <f>IF(C21=0,0,D21/C21)</f>
         <v/>
       </c>
-      <c r="F21" s="16">
-        <f>SUM(F16:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>SUM(G16:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="17">
+      <c r="F21" s="12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H21" s="13">
         <f>F21-G21</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="14">
         <f>IF(G21=0,0,H21/G21)</f>
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>27000</v>
+      </c>
+      <c r="D22" s="9">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(C22=0,0,D22/C22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>85500</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="H22" s="9">
+        <f>F22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>IF(G22=0,0,H22/G22)</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Vehicle Expenses</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D23" s="13">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>IF(C23=0,0,D23/C23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>54500</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H23" s="13">
+        <f>F23-G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>IF(G23=0,0,H23/G23)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Sales &amp; Account Management</t>
+          <t>Office Supplies &amp; Software</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>322000</v>
+        <v>5100</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>314000</v>
+        <v>3500</v>
       </c>
       <c r="D24" s="9">
         <f>B24-C24</f>
@@ -1353,10 +1353,10 @@
         <v/>
       </c>
       <c r="F24" s="8" t="n">
-        <v>953000</v>
+        <v>13100</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>933000</v>
+        <v>10500</v>
       </c>
       <c r="H24" s="9">
         <f>F24-G24</f>
@@ -1370,14 +1370,14 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>General &amp; Administrative</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>269000</v>
+        <v>12000</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>262000</v>
+        <v>5000</v>
       </c>
       <c r="D25" s="13">
         <f>B25-C25</f>
@@ -1388,10 +1388,10 @@
         <v/>
       </c>
       <c r="F25" s="12" t="n">
-        <v>795000</v>
+        <v>24700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>778000</v>
+        <v>15000</v>
       </c>
       <c r="H25" s="13">
         <f>F25-G25</f>
@@ -1405,14 +1405,14 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>IT &amp; Software</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>161000</v>
+        <v>2800</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>157000</v>
+        <v>3000</v>
       </c>
       <c r="D26" s="9">
         <f>B26-C26</f>
@@ -1423,10 +1423,10 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>477000</v>
+        <v>8500</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>466000</v>
+        <v>9000</v>
       </c>
       <c r="H26" s="9">
         <f>F26-G26</f>
@@ -1440,14 +1440,14 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Insurance (Cargo &amp; General)</t>
+          <t>Utilities &amp; Telephone</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>108000</v>
+        <v>3400</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>99000</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="13">
         <f>B27-C27</f>
@@ -1458,10 +1458,10 @@
         <v/>
       </c>
       <c r="F27" s="12" t="n">
-        <v>318000</v>
+        <v>10800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>294000</v>
+        <v>10500</v>
       </c>
       <c r="H27" s="13">
         <f>F27-G27</f>
@@ -1473,425 +1473,320 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Professional Services</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>54000</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>52000</v>
-      </c>
-      <c r="D28" s="9">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>SUM(B20:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>SUM(C20:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="18">
         <f>IF(C28=0,0,D28/C28)</f>
         <v/>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>159000</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>154000</v>
-      </c>
-      <c r="H28" s="9">
+      <c r="F28" s="16">
+        <f>SUM(F20:F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>SUM(G20:G27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
         <f>F28-G28</f>
         <v/>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="18">
         <f>IF(G28=0,0,H28/G28)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n">
-        <v>107000</v>
-      </c>
-      <c r="C29" s="12" t="n">
-        <v>105000</v>
-      </c>
-      <c r="D29" s="13">
-        <f>B29-C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="14">
-        <f>IF(C29=0,0,D29/C29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>315000</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>312000</v>
-      </c>
-      <c r="H29" s="13">
-        <f>F29-G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="14">
-        <f>IF(G29=0,0,H29/G29)</f>
-        <v/>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Other Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>43000</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>42000</v>
-      </c>
-      <c r="D30" s="9">
-        <f>B30-C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>IF(C30=0,0,D30/C30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>127000</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>124000</v>
-      </c>
-      <c r="H30" s="9">
-        <f>F30-G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="10">
-        <f>IF(G30=0,0,H30/G30)</f>
-        <v/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B31" s="16">
-        <f>SUM(B24:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="16">
-        <f>SUM(C24:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" s="9">
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="10">
         <f>IF(C31=0,0,D31/C31)</f>
         <v/>
       </c>
-      <c r="F31" s="16">
-        <f>SUM(F24:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="16">
-        <f>SUM(G24:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="17">
+      <c r="F31" s="8" t="n">
+        <v>3650</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H31" s="9">
         <f>F31-G31</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="10">
         <f>IF(G31=0,0,H31/G31)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>SUM(B31:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>SUM(C31:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>IF(C32=0,0,D32/C32)</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>SUM(F31:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>SUM(G31:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>F32-G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>IF(G32=0,0,H32/G32)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D34" s="9">
-        <f>B34-C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>IF(C34=0,0,D34/C34)</f>
-        <v/>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H34" s="9">
-        <f>F34-G34</f>
-        <v/>
-      </c>
-      <c r="I34" s="10">
-        <f>IF(G34=0,0,H34/G34)</f>
-        <v/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Total Other Income</t>
-        </is>
-      </c>
-      <c r="B35" s="16">
-        <f>SUM(B34:B34)</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="17">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D35" s="9">
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="10">
         <f>IF(C35=0,0,D35/C35)</f>
         <v/>
       </c>
-      <c r="F35" s="16">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>SUM(G34:G34)</f>
-        <v/>
-      </c>
-      <c r="H35" s="17">
+      <c r="F35" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H35" s="9">
         <f>F35-G35</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="10">
         <f>IF(G35=0,0,H35/G35)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Other Expenses</t>
-        </is>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Total Other Expenses</t>
+        </is>
+      </c>
+      <c r="B36" s="16">
+        <f>SUM(B35:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f>IF(C36=0,0,D36/C36)</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>SUM(G35:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>F36-G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="18">
+        <f>IF(G36=0,0,H36/G36)</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>42000</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B38" s="20">
+        <f>B10-B17</f>
+        <v/>
+      </c>
+      <c r="C38" s="20">
+        <f>C10-C17</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
         <f>B38-C38</f>
         <v/>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="22">
         <f>IF(C38=0,0,D38/C38)</f>
         <v/>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="H38" s="9">
+      <c r="F38" s="20">
+        <f>F10-F17</f>
+        <v/>
+      </c>
+      <c r="G38" s="20">
+        <f>G10-G17</f>
+        <v/>
+      </c>
+      <c r="H38" s="21">
         <f>F38-G38</f>
         <v/>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="22">
         <f>IF(G38=0,0,H38/G38)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Total Other Expenses</t>
-        </is>
-      </c>
-      <c r="B39" s="16">
-        <f>SUM(B38:B38)</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>SUM(C38:C38)</f>
-        <v/>
-      </c>
-      <c r="D39" s="17">
-        <f>B39-C39</f>
-        <v/>
-      </c>
-      <c r="E39" s="18">
-        <f>IF(C39=0,0,D39/C39)</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>SUM(F38:F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>SUM(G38:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="17">
-        <f>F39-G39</f>
-        <v/>
-      </c>
-      <c r="I39" s="18">
-        <f>IF(G39=0,0,H39/G39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B41" s="20">
-        <f>B13-B21</f>
-        <v/>
-      </c>
-      <c r="C41" s="20">
-        <f>C13-C21</f>
-        <v/>
-      </c>
-      <c r="D41" s="21">
-        <f>B41-C41</f>
-        <v/>
-      </c>
-      <c r="E41" s="22">
-        <f>IF(C41=0,0,D41/C41)</f>
-        <v/>
-      </c>
-      <c r="F41" s="20">
-        <f>F13-F21</f>
-        <v/>
-      </c>
-      <c r="G41" s="20">
-        <f>G13-G21</f>
-        <v/>
-      </c>
-      <c r="H41" s="21">
-        <f>F41-G41</f>
-        <v/>
-      </c>
-      <c r="I41" s="22">
-        <f>IF(G41=0,0,H41/G41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B43" s="20">
-        <f>B41-B31</f>
-        <v/>
-      </c>
-      <c r="C43" s="20">
-        <f>C41-C31</f>
-        <v/>
-      </c>
-      <c r="D43" s="21">
-        <f>B43-C43</f>
-        <v/>
-      </c>
-      <c r="E43" s="22">
-        <f>IF(C43=0,0,D43/C43)</f>
-        <v/>
-      </c>
-      <c r="F43" s="20">
-        <f>F41-F31</f>
-        <v/>
-      </c>
-      <c r="G43" s="20">
-        <f>G41-G31</f>
-        <v/>
-      </c>
-      <c r="H43" s="21">
-        <f>F43-G43</f>
-        <v/>
-      </c>
-      <c r="I43" s="22">
-        <f>IF(G43=0,0,H43/G43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="B40" s="20">
+        <f>B38-B28</f>
+        <v/>
+      </c>
+      <c r="C40" s="20">
+        <f>C38-C28</f>
+        <v/>
+      </c>
+      <c r="D40" s="21">
+        <f>B40-C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="22">
+        <f>IF(C40=0,0,D40/C40)</f>
+        <v/>
+      </c>
+      <c r="F40" s="20">
+        <f>F38-F28</f>
+        <v/>
+      </c>
+      <c r="G40" s="20">
+        <f>G38-G28</f>
+        <v/>
+      </c>
+      <c r="H40" s="21">
+        <f>F40-G40</f>
+        <v/>
+      </c>
+      <c r="I40" s="22">
+        <f>IF(G40=0,0,H40/G40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B45" s="20">
-        <f>B43+B35-B39</f>
-        <v/>
-      </c>
-      <c r="C45" s="20">
-        <f>C43+C35-C39</f>
-        <v/>
-      </c>
-      <c r="D45" s="21">
-        <f>B45-C45</f>
-        <v/>
-      </c>
-      <c r="E45" s="22">
-        <f>IF(C45=0,0,D45/C45)</f>
-        <v/>
-      </c>
-      <c r="F45" s="20">
-        <f>F43+F35-F39</f>
-        <v/>
-      </c>
-      <c r="G45" s="20">
-        <f>G43+G35-G39</f>
-        <v/>
-      </c>
-      <c r="H45" s="21">
-        <f>F45-G45</f>
-        <v/>
-      </c>
-      <c r="I45" s="22">
-        <f>IF(G45=0,0,H45/G45)</f>
+      <c r="B42" s="20">
+        <f>B40+B32-B36</f>
+        <v/>
+      </c>
+      <c r="C42" s="20">
+        <f>C40+C32-C36</f>
+        <v/>
+      </c>
+      <c r="D42" s="21">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="22">
+        <f>IF(C42=0,0,D42/C42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="20">
+        <f>F40+F32-F36</f>
+        <v/>
+      </c>
+      <c r="G42" s="20">
+        <f>G40+G32-G36</f>
+        <v/>
+      </c>
+      <c r="H42" s="21">
+        <f>F42-G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="22">
+        <f>IF(G42=0,0,H42/G42)</f>
         <v/>
       </c>
     </row>
@@ -1902,7 +1797,7 @@
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7:E45">
+  <conditionalFormatting sqref="E7:E42">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.10</formula>
     </cfRule>
@@ -1918,7 +1813,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I45">
+  <conditionalFormatting sqref="I7:I42">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0.10</formula>
     </cfRule>
@@ -1971,7 +1866,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSM Worldwide</t>
+          <t>Acme Construction LLC</t>
         </is>
       </c>
     </row>
@@ -2044,10 +1939,10 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>10750000</v>
+        <v>1588000</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>10450000</v>
+        <v>1580000</v>
       </c>
       <c r="D6" s="25">
         <f>B6-C6</f>
@@ -2058,10 +1953,10 @@
         <v/>
       </c>
       <c r="F6" s="24" t="n">
-        <v>31790000</v>
+        <v>4570000</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>31085000</v>
+        <v>4440000</v>
       </c>
       <c r="H6" s="25">
         <f>F6-G6</f>
@@ -2079,10 +1974,10 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>8655000</v>
+        <v>1247000</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>8414000</v>
+        <v>1200000</v>
       </c>
       <c r="D7" s="25">
         <f>B7-C7</f>
@@ -2093,10 +1988,10 @@
         <v/>
       </c>
       <c r="F7" s="24" t="n">
-        <v>25591000</v>
+        <v>3502500</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>25028000</v>
+        <v>3362000</v>
       </c>
       <c r="H7" s="25">
         <f>F7-G7</f>
@@ -2114,10 +2009,10 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>2095000</v>
+        <v>341000</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>2036000</v>
+        <v>380000</v>
       </c>
       <c r="D8" s="21">
         <f>B8-C8</f>
@@ -2128,10 +2023,10 @@
         <v/>
       </c>
       <c r="F8" s="20" t="n">
-        <v>6199000</v>
+        <v>1067500</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>6057000</v>
+        <v>1078000</v>
       </c>
       <c r="H8" s="21">
         <f>F8-G8</f>
@@ -2149,10 +2044,10 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>1064000</v>
+        <v>148300</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>1031000</v>
+        <v>131000</v>
       </c>
       <c r="D9" s="25">
         <f>B9-C9</f>
@@ -2163,10 +2058,10 @@
         <v/>
       </c>
       <c r="F9" s="24" t="n">
-        <v>3144000</v>
+        <v>428100</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>3061000</v>
+        <v>393000</v>
       </c>
       <c r="H9" s="25">
         <f>F9-G9</f>
@@ -2184,10 +2079,10 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>1031000</v>
+        <v>192700</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>1005000</v>
+        <v>249000</v>
       </c>
       <c r="D10" s="21">
         <f>B10-C10</f>
@@ -2198,10 +2093,10 @@
         <v/>
       </c>
       <c r="F10" s="20" t="n">
-        <v>3055000</v>
+        <v>639400</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>2996000</v>
+        <v>685000</v>
       </c>
       <c r="H10" s="21">
         <f>F10-G10</f>
@@ -2219,10 +2114,10 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>1001000</v>
+        <v>189000</v>
       </c>
       <c r="C11" s="20" t="n">
-        <v>970000</v>
+        <v>245000</v>
       </c>
       <c r="D11" s="21">
         <f>B11-C11</f>
@@ -2233,10 +2128,10 @@
         <v/>
       </c>
       <c r="F11" s="20" t="n">
-        <v>2961000</v>
+        <v>628650</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>2891000</v>
+        <v>673000</v>
       </c>
       <c r="H11" s="21">
         <f>F11-G11</f>
@@ -2289,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2205,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSM Worldwide</t>
+          <t>Acme Construction LLC</t>
         </is>
       </c>
     </row>
@@ -2406,14 +2301,14 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>Revenue - Chicago HQ</t>
+          <t>Construction Revenue</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10350000</v>
+        <v>4315000</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>10125000</v>
+        <v>4200000</v>
       </c>
       <c r="D7" s="10">
         <f>IF(C7=0,0,(B7-C7)/C7)</f>
@@ -2423,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>10600000</v>
+        <v>4800000</v>
       </c>
       <c r="G7" s="10">
         <f>IF(F7=0,0,(E7-F7)/F7)</f>
@@ -2433,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>10950000</v>
+        <v>5250000</v>
       </c>
       <c r="J7" s="10">
         <f>IF(I7=0,0,(H7-I7)/I7)</f>
@@ -2443,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>11300000</v>
+        <v>4050000</v>
       </c>
       <c r="M7" s="10">
         <f>IF(L7=0,0,(K7-L7)/L7)</f>
@@ -2453,14 +2348,14 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Revenue - Atlanta</t>
+          <t>Service &amp; Maintenance Revenue</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>6900000</v>
+        <v>255000</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>6750000</v>
+        <v>240000</v>
       </c>
       <c r="D8" s="14">
         <f>IF(C8=0,0,(B8-C8)/C8)</f>
@@ -2470,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>7070000</v>
+        <v>260000</v>
       </c>
       <c r="G8" s="14">
         <f>IF(F8=0,0,(E8-F8)/F8)</f>
@@ -2480,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>7300000</v>
+        <v>265000</v>
       </c>
       <c r="J8" s="14">
         <f>IF(I8=0,0,(H8-I8)/I8)</f>
@@ -2490,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>7520000</v>
+        <v>230000</v>
       </c>
       <c r="M8" s="14">
         <f>IF(L8=0,0,(K8-L8)/L8)</f>
@@ -2498,407 +2393,328 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>Revenue - Dallas</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>5920000</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>5770000</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="16">
+        <f>SUM(B7:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="18">
         <f>IF(C9=0,0,(B9-C9)/C9)</f>
         <v/>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>6060000</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="E9" s="16">
+        <f>SUM(E7:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
         <f>IF(F9=0,0,(E9-F9)/F9)</f>
         <v/>
       </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>6260000</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="H9" s="16">
+        <f>SUM(H7:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="16">
+        <f>SUM(I7:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="18">
         <f>IF(I9=0,0,(H9-I9)/I9)</f>
         <v/>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>6450000</v>
-      </c>
-      <c r="M9" s="10">
+      <c r="K9" s="16">
+        <f>SUM(K7:K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="16">
+        <f>SUM(L7:L8)</f>
+        <v/>
+      </c>
+      <c r="M9" s="18">
         <f>IF(L9=0,0,(K9-L9)/L9)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Revenue - Las Vegas</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>4430000</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>4330000</v>
-      </c>
-      <c r="D10" s="14">
-        <f>IF(C10=0,0,(B10-C10)/C10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>4540000</v>
-      </c>
-      <c r="G10" s="14">
-        <f>IF(F10=0,0,(E10-F10)/F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>4690000</v>
-      </c>
-      <c r="J10" s="14">
-        <f>IF(I10=0,0,(H10-I10)/I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>4840000</v>
-      </c>
-      <c r="M10" s="14">
-        <f>IF(L10=0,0,(K10-L10)/L10)</f>
-        <v/>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Revenue - York PA</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>4190000</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>4110000</v>
-      </c>
-      <c r="D11" s="10">
-        <f>IF(C11=0,0,(B11-C11)/C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="G11" s="10">
-        <f>IF(F11=0,0,(E11-F11)/F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>4440000</v>
-      </c>
-      <c r="J11" s="10">
-        <f>IF(I11=0,0,(H11-I11)/I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>4580000</v>
-      </c>
-      <c r="M11" s="10">
-        <f>IF(L11=0,0,(K11-L11)/L11)</f>
-        <v/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B12" s="16">
-        <f>SUM(B7:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="16">
-        <f>SUM(C7:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="18">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Direct Labor</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1459000</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="D12" s="10">
         <f>IF(C12=0,0,(B12-C12)/C12)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
-        <f>SUM(E7:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
-        <f>SUM(F7:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="18">
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="G12" s="10">
         <f>IF(F12=0,0,(E12-F12)/F12)</f>
         <v/>
       </c>
-      <c r="H12" s="16">
-        <f>SUM(H7:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="16">
-        <f>SUM(I7:I11)</f>
-        <v/>
-      </c>
-      <c r="J12" s="18">
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>1784000</v>
+      </c>
+      <c r="J12" s="10">
         <f>IF(I12=0,0,(H12-I12)/I12)</f>
         <v/>
       </c>
-      <c r="K12" s="16">
-        <f>SUM(K7:K11)</f>
-        <v/>
-      </c>
-      <c r="L12" s="16">
-        <f>SUM(L7:L11)</f>
-        <v/>
-      </c>
-      <c r="M12" s="18">
+      <c r="K12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>1378000</v>
+      </c>
+      <c r="M12" s="10">
         <f>IF(L12=0,0,(K12-L12)/L12)</f>
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1255000</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>1176000</v>
+      </c>
+      <c r="D13" s="14">
+        <f>IF(C13=0,0,(B13-C13)/C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>1344000</v>
+      </c>
+      <c r="G13" s="14">
+        <f>IF(F13=0,0,(E13-F13)/F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="J13" s="14">
+        <f>IF(I13=0,0,(H13-I13)/I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>1134000</v>
+      </c>
+      <c r="M13" s="14">
+        <f>IF(L13=0,0,(K13-L13)/L13)</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>663000</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>630000</v>
+      </c>
+      <c r="D14" s="10">
+        <f>IF(C14=0,0,(B14-C14)/C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>720000</v>
+      </c>
+      <c r="G14" s="10">
+        <f>IF(F14=0,0,(E14-F14)/F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>787500</v>
+      </c>
+      <c r="J14" s="10">
+        <f>IF(I14=0,0,(H14-I14)/I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>607500</v>
+      </c>
+      <c r="M14" s="10">
+        <f>IF(L14=0,0,(K14-L14)/L14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Carrier &amp; Freight Costs</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>17484000</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>17097000</v>
-      </c>
-      <c r="D15" s="10">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Equipment Costs</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>125500</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>126000</v>
+      </c>
+      <c r="D15" s="14">
         <f>IF(C15=0,0,(B15-C15)/C15)</f>
         <v/>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>17911000</v>
-      </c>
-      <c r="G15" s="10">
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>144000</v>
+      </c>
+      <c r="G15" s="14">
         <f>IF(F15=0,0,(E15-F15)/F15)</f>
         <v/>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>18520000</v>
-      </c>
-      <c r="J15" s="10">
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>157500</v>
+      </c>
+      <c r="J15" s="14">
         <f>IF(I15=0,0,(H15-I15)/I15)</f>
         <v/>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>19084000</v>
-      </c>
-      <c r="M15" s="10">
+      <c r="K15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>121500</v>
+      </c>
+      <c r="M15" s="14">
         <f>IF(L15=0,0,(K15-L15)/L15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Sort &amp; Distribution Labor</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>5722000</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>5595000</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Total Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>SUM(B12:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>SUM(C12:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
         <f>IF(C16=0,0,(B16-C16)/C16)</f>
         <v/>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>5861000</v>
-      </c>
-      <c r="G16" s="14">
+      <c r="E16" s="16">
+        <f>SUM(E12:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>SUM(F12:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="18">
         <f>IF(F16=0,0,(E16-F16)/F16)</f>
         <v/>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>6061000</v>
-      </c>
-      <c r="J16" s="14">
+      <c r="H16" s="16">
+        <f>SUM(H12:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>SUM(I12:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="18">
         <f>IF(I16=0,0,(H16-I16)/I16)</f>
         <v/>
       </c>
-      <c r="K16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>6243000</v>
-      </c>
-      <c r="M16" s="14">
+      <c r="K16" s="16">
+        <f>SUM(K12:K15)</f>
+        <v/>
+      </c>
+      <c r="L16" s="16">
+        <f>SUM(L12:L15)</f>
+        <v/>
+      </c>
+      <c r="M16" s="18">
         <f>IF(L16=0,0,(K16-L16)/L16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Facility &amp; Warehouse Costs</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>1589000</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>1558000</v>
-      </c>
-      <c r="D17" s="10">
-        <f>IF(C17=0,0,(B17-C17)/C17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>1633000</v>
-      </c>
-      <c r="G17" s="10">
-        <f>IF(F17=0,0,(E17-F17)/F17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>1688000</v>
-      </c>
-      <c r="J17" s="10">
-        <f>IF(I17=0,0,(H17-I17)/I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>1739000</v>
-      </c>
-      <c r="M17" s="10">
-        <f>IF(L17=0,0,(K17-L17)/L17)</f>
-        <v/>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Packaging &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>477000</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>466000</v>
-      </c>
-      <c r="D18" s="14">
-        <f>IF(C18=0,0,(B18-C18)/C18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>489000</v>
-      </c>
-      <c r="G18" s="14">
-        <f>IF(F18=0,0,(E18-F18)/F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>505000</v>
-      </c>
-      <c r="J18" s="14">
-        <f>IF(I18=0,0,(H18-I18)/I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>520000</v>
-      </c>
-      <c r="M18" s="14">
-        <f>IF(L18=0,0,(K18-L18)/L18)</f>
-        <v/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>Technology &amp; Tracking Systems</t>
+          <t>Office Rent</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>319000</v>
+        <v>36000</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>312000</v>
+        <v>36000</v>
       </c>
       <c r="D19" s="10">
         <f>IF(C19=0,0,(B19-C19)/C19)</f>
@@ -2908,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>326000</v>
+        <v>36000</v>
       </c>
       <c r="G19" s="10">
         <f>IF(F19=0,0,(E19-F19)/F19)</f>
@@ -2918,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>337000</v>
+        <v>36000</v>
       </c>
       <c r="J19" s="10">
         <f>IF(I19=0,0,(H19-I19)/I19)</f>
@@ -2928,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>348000</v>
+        <v>36000</v>
       </c>
       <c r="M19" s="10">
         <f>IF(L19=0,0,(K19-L19)/L19)</f>
@@ -2936,78 +2752,157 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Total Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B20" s="16">
-        <f>SUM(B15:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="16">
-        <f>SUM(C15:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="18">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Administrative Salaries</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>186000</v>
+      </c>
+      <c r="D20" s="14">
         <f>IF(C20=0,0,(B20-C20)/C20)</f>
         <v/>
       </c>
-      <c r="E20" s="16">
-        <f>SUM(E15:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="16">
-        <f>SUM(F15:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="18">
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G20" s="14">
         <f>IF(F20=0,0,(E20-F20)/F20)</f>
         <v/>
       </c>
-      <c r="H20" s="16">
-        <f>SUM(H15:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="16">
-        <f>SUM(I15:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="18">
+      <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="J20" s="14">
         <f>IF(I20=0,0,(H20-I20)/I20)</f>
         <v/>
       </c>
-      <c r="K20" s="16">
-        <f>SUM(K15:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="16">
-        <f>SUM(L15:L19)</f>
-        <v/>
-      </c>
-      <c r="M20" s="18">
+      <c r="K20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>195000</v>
+      </c>
+      <c r="M20" s="14">
         <f>IF(L20=0,0,(K20-L20)/L20)</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>85500</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="D21" s="10">
+        <f>IF(C21=0,0,(B21-C21)/C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="G21" s="10">
+        <f>IF(F21=0,0,(E21-F21)/F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="J21" s="10">
+        <f>IF(I21=0,0,(H21-I21)/I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="M21" s="10">
+        <f>IF(L21=0,0,(K21-L21)/L21)</f>
+        <v/>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Vehicle Expenses</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>54500</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D22" s="14">
+        <f>IF(C22=0,0,(B22-C22)/C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>51000</v>
+      </c>
+      <c r="G22" s="14">
+        <f>IF(F22=0,0,(E22-F22)/F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>51000</v>
+      </c>
+      <c r="J22" s="14">
+        <f>IF(I22=0,0,(H22-I22)/I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M22" s="14">
+        <f>IF(L22=0,0,(K22-L22)/L22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Sales &amp; Account Management</t>
+          <t>Office Supplies &amp; Software</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>953000</v>
+        <v>13100</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>933000</v>
+        <v>10500</v>
       </c>
       <c r="D23" s="10">
         <f>IF(C23=0,0,(B23-C23)/C23)</f>
@@ -3017,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>977000</v>
+        <v>10500</v>
       </c>
       <c r="G23" s="10">
         <f>IF(F23=0,0,(E23-F23)/F23)</f>
@@ -3027,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>1011000</v>
+        <v>10500</v>
       </c>
       <c r="J23" s="10">
         <f>IF(I23=0,0,(H23-I23)/I23)</f>
@@ -3037,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1040000</v>
+        <v>10500</v>
       </c>
       <c r="M23" s="10">
         <f>IF(L23=0,0,(K23-L23)/L23)</f>
@@ -3047,14 +2942,14 @@
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>General &amp; Administrative</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>795000</v>
+        <v>24700</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>778000</v>
+        <v>15000</v>
       </c>
       <c r="D24" s="14">
         <f>IF(C24=0,0,(B24-C24)/C24)</f>
@@ -3064,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>815000</v>
+        <v>15000</v>
       </c>
       <c r="G24" s="14">
         <f>IF(F24=0,0,(E24-F24)/F24)</f>
@@ -3074,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>843000</v>
+        <v>15000</v>
       </c>
       <c r="J24" s="14">
         <f>IF(I24=0,0,(H24-I24)/I24)</f>
@@ -3084,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>868000</v>
+        <v>15000</v>
       </c>
       <c r="M24" s="14">
         <f>IF(L24=0,0,(K24-L24)/L24)</f>
@@ -3094,14 +2989,14 @@
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>IT &amp; Software</t>
+          <t>Advertising &amp; Marketing</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>477000</v>
+        <v>8500</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>466000</v>
+        <v>9000</v>
       </c>
       <c r="D25" s="10">
         <f>IF(C25=0,0,(B25-C25)/C25)</f>
@@ -3111,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>489000</v>
+        <v>11000</v>
       </c>
       <c r="G25" s="10">
         <f>IF(F25=0,0,(E25-F25)/F25)</f>
@@ -3121,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>505000</v>
+        <v>11000</v>
       </c>
       <c r="J25" s="10">
         <f>IF(I25=0,0,(H25-I25)/I25)</f>
@@ -3131,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>520000</v>
+        <v>9000</v>
       </c>
       <c r="M25" s="10">
         <f>IF(L25=0,0,(K25-L25)/L25)</f>
@@ -3141,14 +3036,14 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>Insurance (Cargo &amp; General)</t>
+          <t>Utilities &amp; Telephone</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>318000</v>
+        <v>10800</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>294000</v>
+        <v>10500</v>
       </c>
       <c r="D26" s="14">
         <f>IF(C26=0,0,(B26-C26)/C26)</f>
@@ -3158,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>307000</v>
+        <v>10500</v>
       </c>
       <c r="G26" s="14">
         <f>IF(F26=0,0,(E26-F26)/F26)</f>
@@ -3168,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>318000</v>
+        <v>10500</v>
       </c>
       <c r="J26" s="14">
         <f>IF(I26=0,0,(H26-I26)/I26)</f>
@@ -3178,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>326000</v>
+        <v>10500</v>
       </c>
       <c r="M26" s="14">
         <f>IF(L26=0,0,(K26-L26)/L26)</f>
@@ -3186,416 +3081,275 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Professional Services</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>159000</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>154000</v>
-      </c>
-      <c r="D27" s="10">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>SUM(B19:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>SUM(C19:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
         <f>IF(C27=0,0,(B27-C27)/C27)</f>
         <v/>
       </c>
-      <c r="E27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>162000</v>
-      </c>
-      <c r="G27" s="10">
+      <c r="E27" s="16">
+        <f>SUM(E19:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="16">
+        <f>SUM(F19:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="18">
         <f>IF(F27=0,0,(E27-F27)/F27)</f>
         <v/>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>168000</v>
-      </c>
-      <c r="J27" s="10">
+      <c r="H27" s="16">
+        <f>SUM(H19:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>SUM(I19:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="18">
         <f>IF(I27=0,0,(H27-I27)/I27)</f>
         <v/>
       </c>
-      <c r="K27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>172000</v>
-      </c>
-      <c r="M27" s="10">
+      <c r="K27" s="16">
+        <f>SUM(K19:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="16">
+        <f>SUM(L19:L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="18">
         <f>IF(L27=0,0,(K27-L27)/L27)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Depreciation &amp; Amortization</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>315000</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>312000</v>
-      </c>
-      <c r="D28" s="14">
-        <f>IF(C28=0,0,(B28-C28)/C28)</f>
-        <v/>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>326000</v>
-      </c>
-      <c r="G28" s="14">
-        <f>IF(F28=0,0,(E28-F28)/F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>337000</v>
-      </c>
-      <c r="J28" s="14">
-        <f>IF(I28=0,0,(H28-I28)/I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>348000</v>
-      </c>
-      <c r="M28" s="14">
-        <f>IF(L28=0,0,(K28-L28)/L28)</f>
-        <v/>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Other Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>127000</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>124000</v>
-      </c>
-      <c r="D29" s="10">
-        <f>IF(C29=0,0,(B29-C29)/C29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>130000</v>
-      </c>
-      <c r="G29" s="10">
-        <f>IF(F29=0,0,(E29-F29)/F29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="J29" s="10">
-        <f>IF(I29=0,0,(H29-I29)/I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>138000</v>
-      </c>
-      <c r="M29" s="10">
-        <f>IF(L29=0,0,(K29-L29)/L29)</f>
-        <v/>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B30" s="16">
-        <f>SUM(B23:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="16">
-        <f>SUM(C23:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>3650</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D30" s="10">
         <f>IF(C30=0,0,(B30-C30)/C30)</f>
         <v/>
       </c>
-      <c r="E30" s="16">
-        <f>SUM(E23:E29)</f>
-        <v/>
-      </c>
-      <c r="F30" s="16">
-        <f>SUM(F23:F29)</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
+      <c r="E30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G30" s="10">
         <f>IF(F30=0,0,(E30-F30)/F30)</f>
         <v/>
       </c>
-      <c r="H30" s="16">
-        <f>SUM(H23:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="16">
-        <f>SUM(I23:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="18">
+      <c r="H30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J30" s="10">
         <f>IF(I30=0,0,(H30-I30)/I30)</f>
         <v/>
       </c>
-      <c r="K30" s="16">
-        <f>SUM(K23:K29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="16">
-        <f>SUM(L23:L29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="18">
+      <c r="K30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M30" s="10">
         <f>IF(L30=0,0,(K30-L30)/L30)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Total Other Income</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>SUM(B30:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>SUM(C30:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f>IF(C31=0,0,(B31-C31)/C31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>SUM(E30:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>SUM(F30:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="18">
+        <f>IF(F31=0,0,(E31-F31)/F31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>SUM(H30:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="16">
+        <f>SUM(I30:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="18">
+        <f>IF(I31=0,0,(H31-I31)/I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>SUM(K30:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="16">
+        <f>SUM(L30:L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="18">
+        <f>IF(L31=0,0,(K31-L31)/L31)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D33" s="10">
-        <f>IF(C33=0,0,(B33-C33)/C33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G33" s="10">
-        <f>IF(F33=0,0,(E33-F33)/F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J33" s="10">
-        <f>IF(I33=0,0,(H33-I33)/I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="M33" s="10">
-        <f>IF(L33=0,0,(K33-L33)/L33)</f>
-        <v/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Total Other Income</t>
-        </is>
-      </c>
-      <c r="B34" s="16">
-        <f>SUM(B33:B33)</f>
-        <v/>
-      </c>
-      <c r="C34" s="16">
-        <f>SUM(C33:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D34" s="10">
         <f>IF(C34=0,0,(B34-C34)/C34)</f>
         <v/>
       </c>
-      <c r="E34" s="16">
-        <f>SUM(E33:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>SUM(F33:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="18">
+      <c r="E34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G34" s="10">
         <f>IF(F34=0,0,(E34-F34)/F34)</f>
         <v/>
       </c>
-      <c r="H34" s="16">
-        <f>SUM(H33:H33)</f>
-        <v/>
-      </c>
-      <c r="I34" s="16">
-        <f>SUM(I33:I33)</f>
-        <v/>
-      </c>
-      <c r="J34" s="18">
+      <c r="H34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J34" s="10">
         <f>IF(I34=0,0,(H34-I34)/I34)</f>
         <v/>
       </c>
-      <c r="K34" s="16">
-        <f>SUM(K33:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="16">
-        <f>SUM(L33:L33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="18">
+      <c r="K34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M34" s="10">
         <f>IF(L34=0,0,(K34-L34)/L34)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Other Expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>129000</v>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="D37" s="10">
-        <f>IF(C37=0,0,(B37-C37)/C37)</f>
-        <v/>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="G37" s="10">
-        <f>IF(F37=0,0,(E37-F37)/F37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="J37" s="10">
-        <f>IF(I37=0,0,(H37-I37)/I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="M37" s="10">
-        <f>IF(L37=0,0,(K37-L37)/L37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Total Other Expenses</t>
         </is>
       </c>
-      <c r="B38" s="16">
-        <f>SUM(B37:B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>SUM(C37:C37)</f>
-        <v/>
-      </c>
-      <c r="D38" s="18">
-        <f>IF(C38=0,0,(B38-C38)/C38)</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>SUM(E37:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>SUM(F37:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="18">
-        <f>IF(F38=0,0,(E38-F38)/F38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="16">
-        <f>SUM(H37:H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="16">
-        <f>SUM(I37:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="18">
-        <f>IF(I38=0,0,(H38-I38)/I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="16">
-        <f>SUM(K37:K37)</f>
-        <v/>
-      </c>
-      <c r="L38" s="16">
-        <f>SUM(L37:L37)</f>
-        <v/>
-      </c>
-      <c r="M38" s="18">
-        <f>IF(L38=0,0,(K38-L38)/L38)</f>
+      <c r="B35" s="16">
+        <f>SUM(B34:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>SUM(C34:C34)</f>
+        <v/>
+      </c>
+      <c r="D35" s="18">
+        <f>IF(C35=0,0,(B35-C35)/C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>SUM(E34:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>SUM(F34:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="18">
+        <f>IF(F35=0,0,(E35-F35)/F35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>SUM(H34:H34)</f>
+        <v/>
+      </c>
+      <c r="I35" s="16">
+        <f>SUM(I34:I34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="18">
+        <f>IF(I35=0,0,(H35-I35)/I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
+        <f>SUM(K34:K34)</f>
+        <v/>
+      </c>
+      <c r="L35" s="16">
+        <f>SUM(L34:L34)</f>
+        <v/>
+      </c>
+      <c r="M35" s="18">
+        <f>IF(L35=0,0,(K35-L35)/L35)</f>
         <v/>
       </c>
     </row>
@@ -3605,7 +3359,7 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D40">
+  <conditionalFormatting sqref="D6:D37">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3613,7 +3367,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G40">
+  <conditionalFormatting sqref="G6:G37">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3621,7 +3375,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J40">
+  <conditionalFormatting sqref="J6:J37">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3629,7 +3383,7 @@
       <formula>-0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M40">
+  <conditionalFormatting sqref="M6:M37">
     <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
       <formula>0.05</formula>
     </cfRule>
@@ -3670,7 +3424,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSM Worldwide</t>
+          <t>Acme Construction LLC</t>
         </is>
       </c>
     </row>
@@ -3763,13 +3517,13 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>10290000</v>
+        <v>1505000</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>10750000</v>
+        <v>1477000</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>10750000</v>
+        <v>1588000</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0</v>
@@ -3806,40 +3560,40 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10280000</v>
+        <v>1430000</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>10355000</v>
+        <v>1430000</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>10450000</v>
+        <v>1580000</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>10600000</v>
+        <v>1585000</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>10910000</v>
+        <v>1735000</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>11060000</v>
+        <v>1740000</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>11200000</v>
+        <v>1890000</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>11380000</v>
+        <v>1890000</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>11060000</v>
+        <v>1735000</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>10750000</v>
+        <v>1580000</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>11670000</v>
+        <v>1425000</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>12270000</v>
+        <v>1275000</v>
       </c>
     </row>
     <row r="8">
@@ -3904,13 +3658,13 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1978000</v>
+        <v>360000</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2126000</v>
+        <v>366500</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>2095000</v>
+        <v>341000</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>0</v>
@@ -3947,40 +3701,40 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2003000</v>
+        <v>349000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2018000</v>
+        <v>349000</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2036000</v>
+        <v>380000</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2066000</v>
+        <v>385000</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2129000</v>
+        <v>416000</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2155000</v>
+        <v>421000</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2171000</v>
+        <v>450000</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>2203000</v>
+        <v>450000</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2155000</v>
+        <v>416000</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2094000</v>
+        <v>380000</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2271000</v>
+        <v>344000</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2391000</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="11">
@@ -4045,13 +3799,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>937000</v>
+        <v>217300</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1087000</v>
+        <v>229400</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1031000</v>
+        <v>192700</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>0</v>
@@ -4088,40 +3842,40 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>992000</v>
+        <v>218000</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>999000</v>
+        <v>218000</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>1005000</v>
+        <v>249000</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1023000</v>
+        <v>251000</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1055000</v>
+        <v>278000</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>1066000</v>
+        <v>283000</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1066000</v>
+        <v>312000</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>1080000</v>
+        <v>312000</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>1066000</v>
+        <v>282000</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1037000</v>
+        <v>246000</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>1123000</v>
+        <v>210000</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>1184000</v>
+        <v>181000</v>
       </c>
     </row>
     <row r="14">
@@ -4186,13 +3940,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>904000</v>
+        <v>213700</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>1056000</v>
+        <v>225950</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>1001000</v>
+        <v>189000</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
@@ -4229,40 +3983,40 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>957000</v>
+        <v>214000</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>964000</v>
+        <v>214000</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>970000</v>
+        <v>245000</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>988000</v>
+        <v>247000</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1020000</v>
+        <v>274000</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1031000</v>
+        <v>279000</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1031000</v>
+        <v>308000</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1045000</v>
+        <v>308000</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>1031000</v>
+        <v>278000</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>1002000</v>
+        <v>242000</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>1088000</v>
+        <v>206000</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>1149000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="17">
